--- a/data/trans_dic/P2A_fisi_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,55; 9,87</t>
+          <t>6,57; 10,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,0; 15,98</t>
+          <t>10,72; 15,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 10,59</t>
+          <t>6,32; 10,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,74; 26,27</t>
+          <t>19,32; 26,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,09; 11,32</t>
+          <t>8,08; 11,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,44; 15,11</t>
+          <t>11,19; 15,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,84; 15,59</t>
+          <t>10,83; 15,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,21; 25,66</t>
+          <t>21,38; 25,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,86; 10,14</t>
+          <t>7,92; 10,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,56; 14,61</t>
+          <t>11,72; 14,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,48; 12,5</t>
+          <t>9,56; 12,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,21; 25,21</t>
+          <t>21,26; 24,9</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,71</t>
+          <t>2,82; 4,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 6,5</t>
+          <t>4,24; 6,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,25</t>
+          <t>4,13; 6,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 10,43</t>
+          <t>6,27; 10,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,97</t>
+          <t>3,08; 5,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 8,55</t>
+          <t>6,01; 8,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,8</t>
+          <t>3,8; 5,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 40,2</t>
+          <t>7,81; 37,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,47</t>
+          <t>3,2; 4,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 6,97</t>
+          <t>5,38; 6,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 5,6</t>
+          <t>4,22; 5,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 26,93</t>
+          <t>8,03; 26,84</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,68</t>
+          <t>1,5; 4,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,08</t>
+          <t>2,22; 6,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,49</t>
+          <t>2,18; 5,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,87</t>
+          <t>4,85; 9,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 7,27</t>
+          <t>3,06; 7,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,07</t>
+          <t>3,11; 7,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,88</t>
+          <t>2,48; 5,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 6,8</t>
+          <t>3,94; 6,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,11</t>
+          <t>2,67; 5,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,25</t>
+          <t>3,08; 6,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,07</t>
+          <t>2,79; 5,26</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 7,52</t>
+          <t>4,93; 7,58</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 5,83</t>
+          <t>4,3; 5,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,39; 8,47</t>
+          <t>6,43; 8,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 6,36</t>
+          <t>4,75; 6,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,25; 11,83</t>
+          <t>8,27; 11,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 7,13</t>
+          <t>5,49; 7,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 10,18</t>
+          <t>8,11; 10,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 7,8</t>
+          <t>6,04; 7,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 31,71</t>
+          <t>10,71; 31,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,25</t>
+          <t>5,13; 6,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 8,85</t>
+          <t>7,56; 8,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 6,85</t>
+          <t>5,66; 6,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,35; 22,89</t>
+          <t>10,37; 22,71</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>67564; 101808</t>
+          <t>67787; 103343</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107221; 155793</t>
+          <t>104492; 150758</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48936; 79865</t>
+          <t>47647; 79287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>101623; 135300</t>
+          <t>99502; 134800</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>106452; 148929</t>
+          <t>106244; 147235</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>153040; 202078</t>
+          <t>149752; 205514</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>107776; 155041</t>
+          <t>107763; 153342</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>160243; 193838</t>
+          <t>161565; 195646</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>184507; 237953</t>
+          <t>185791; 241390</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>267263; 337761</t>
+          <t>270927; 337143</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165751; 218566</t>
+          <t>167213; 221163</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>269413; 320293</t>
+          <t>270145; 316380</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>48845; 79706</t>
+          <t>47831; 78637</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87527; 127640</t>
+          <t>83202; 126043</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86897; 129845</t>
+          <t>85850; 125950</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>142074; 238856</t>
+          <t>143677; 242223</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47284; 78884</t>
+          <t>48871; 80175</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>105476; 150353</t>
+          <t>105581; 150908</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75488; 115378</t>
+          <t>75583; 114744</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>174852; 899709</t>
+          <t>174700; 838316</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>104330; 146647</t>
+          <t>104850; 147697</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200789; 259555</t>
+          <t>200411; 259832</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>169775; 227773</t>
+          <t>171670; 226853</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>366860; 1219303</t>
+          <t>363774; 1215187</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8485; 25786</t>
+          <t>8272; 26866</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11075; 29239</t>
+          <t>10700; 30821</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11597; 30001</t>
+          <t>11922; 32072</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32716; 63809</t>
+          <t>31359; 62444</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14734; 34626</t>
+          <t>14559; 34171</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15379; 37034</t>
+          <t>14273; 34697</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13669; 32315</t>
+          <t>13631; 32470</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26034; 44884</t>
+          <t>26044; 45693</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26091; 52555</t>
+          <t>27439; 52956</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29781; 58752</t>
+          <t>28991; 57348</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29915; 55620</t>
+          <t>30628; 57610</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>62852; 98330</t>
+          <t>64486; 99076</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>139518; 191126</t>
+          <t>140911; 188514</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>218668; 289557</t>
+          <t>219790; 283323</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>162824; 214731</t>
+          <t>160574; 214788</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>284731; 408401</t>
+          <t>285403; 410474</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>183046; 240842</t>
+          <t>185394; 242778</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>287923; 361708</t>
+          <t>288167; 360029</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>212349; 275438</t>
+          <t>213301; 275470</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>388086; 1158747</t>
+          <t>391228; 1158887</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>338131; 415727</t>
+          <t>341330; 414212</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>523709; 616876</t>
+          <t>527182; 622719</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>388292; 473126</t>
+          <t>391077; 470440</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>735125; 1626636</t>
+          <t>736870; 1613918</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_fisi_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,02</t>
+          <t>6,7; 10,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,52 +727,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 10,51</t>
+          <t>6,61; 10,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,32; 26,18</t>
+          <t>18,53; 25,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,08; 11,2</t>
+          <t>8,1; 11,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,19; 15,36</t>
+          <t>11,26; 15,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,83; 15,42</t>
+          <t>10,79; 15,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,38; 25,9</t>
+          <t>21,58; 26,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,92; 10,29</t>
+          <t>7,95; 10,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,72; 14,58</t>
+          <t>11,59; 14,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 12,65</t>
+          <t>9,29; 12,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,26; 24,9</t>
+          <t>20,84; 24,65</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,64</t>
+          <t>2,96; 4,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,42</t>
+          <t>4,35; 6,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 6,07</t>
+          <t>4,07; 5,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 10,58</t>
+          <t>8,24; 10,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,05</t>
+          <t>2,96; 5,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 8,59</t>
+          <t>5,98; 8,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,77</t>
+          <t>3,73; 5,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 37,46</t>
+          <t>7,83; 10,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,5</t>
+          <t>3,19; 4,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 6,98</t>
+          <t>5,38; 7,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 5,58</t>
+          <t>4,17; 5,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 26,84</t>
+          <t>8,32; 10,07</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,87</t>
+          <t>1,57; 4,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,41</t>
+          <t>2,23; 6,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,86</t>
+          <t>2,09; 5,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,66</t>
+          <t>5,0; 9,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,17</t>
+          <t>3,06; 7,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,57</t>
+          <t>3,25; 7,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,91</t>
+          <t>2,48; 5,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 6,92</t>
+          <t>4,27; 7,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,15</t>
+          <t>2,67; 5,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,1</t>
+          <t>3,2; 6,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,26</t>
+          <t>2,64; 5,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,58</t>
+          <t>4,98; 7,66</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -1137,52 +1137,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 5,75</t>
+          <t>4,23; 5,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 8,28</t>
+          <t>6,44; 8,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,36</t>
+          <t>4,78; 6,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,89</t>
+          <t>9,82; 11,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,18</t>
+          <t>5,4; 7,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 10,13</t>
+          <t>8,1; 10,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 7,8</t>
+          <t>6,08; 7,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,71; 31,72</t>
+          <t>10,62; 12,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 6,22</t>
+          <t>5,08; 6,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,56; 8,93</t>
+          <t>7,55; 8,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,37; 22,71</t>
+          <t>10,55; 11,87</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116353</t>
+          <t>123049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>177802</t>
+          <t>194599</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>294155</t>
+          <t>317648</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>67787; 103343</t>
+          <t>69158; 104935</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>104492; 150758</t>
+          <t>104507; 150796</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47647; 79287</t>
+          <t>49871; 80078</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99502; 134800</t>
+          <t>107182; 145260</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>106244; 147235</t>
+          <t>106585; 149218</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>149752; 205514</t>
+          <t>150597; 203421</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>107763; 153342</t>
+          <t>107289; 152034</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>161565; 195646</t>
+          <t>177429; 215470</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>185791; 241390</t>
+          <t>186603; 241330</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>270927; 337143</t>
+          <t>267985; 335120</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167213; 221163</t>
+          <t>162438; 220204</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>270145; 316380</t>
+          <t>291829; 345190</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>200233</t>
+          <t>211159</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>371494</t>
+          <t>192035</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>571727</t>
+          <t>403194</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47831; 78637</t>
+          <t>50116; 79769</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83202; 126043</t>
+          <t>85497; 125582</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85850; 125950</t>
+          <t>84407; 124260</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>143677; 242223</t>
+          <t>183890; 239235</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48871; 80175</t>
+          <t>47056; 79569</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>105581; 150908</t>
+          <t>105097; 151554</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75583; 114744</t>
+          <t>74170; 113456</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>174700; 838316</t>
+          <t>170051; 218551</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>104850; 147697</t>
+          <t>104666; 150493</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200411; 259832</t>
+          <t>200211; 261540</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>171670; 226853</t>
+          <t>169554; 224875</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>363774; 1215187</t>
+          <t>366408; 443083</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45405</t>
+          <t>49468</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34223</t>
+          <t>40112</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79628</t>
+          <t>89580</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8272; 26866</t>
+          <t>8672; 26275</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10700; 30821</t>
+          <t>10747; 29869</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11922; 32072</t>
+          <t>11403; 29769</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31359; 62444</t>
+          <t>35592; 68172</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14559; 34171</t>
+          <t>14590; 35571</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14273; 34697</t>
+          <t>14902; 35521</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13631; 32470</t>
+          <t>13618; 32404</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26044; 45693</t>
+          <t>31398; 52670</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27439; 52956</t>
+          <t>27471; 53750</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28991; 57348</t>
+          <t>30042; 59123</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30628; 57610</t>
+          <t>28935; 56694</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64486; 99076</t>
+          <t>72034; 110866</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361991</t>
+          <t>383676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>583519</t>
+          <t>426747</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>945510</t>
+          <t>810422</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>140911; 188514</t>
+          <t>138475; 189999</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>219790; 283323</t>
+          <t>220195; 284922</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>160574; 214788</t>
+          <t>161544; 216733</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>285403; 410474</t>
+          <t>345689; 422247</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>185394; 242778</t>
+          <t>182438; 241226</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>288167; 360029</t>
+          <t>287995; 358518</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>213301; 275470</t>
+          <t>214667; 276003</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>391228; 1158887</t>
+          <t>396069; 463170</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>341330; 414212</t>
+          <t>338008; 411953</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>527182; 622719</t>
+          <t>526227; 617423</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>391077; 470440</t>
+          <t>390782; 470528</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>736870; 1613918</t>
+          <t>764862; 860632</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_fisi_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
